--- a/Laporan_Forward_Testing_Model_Terbaru_SMC.xlsx
+++ b/Laporan_Forward_Testing_Model_Terbaru_SMC.xlsx
@@ -966,7 +966,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 13:33:54 WIB</t>
+          <t>2026-09-09 13:45:00 WIB</t>
         </is>
       </c>
     </row>

--- a/Laporan_Forward_Testing_Model_Terbaru_SMC.xlsx
+++ b/Laporan_Forward_Testing_Model_Terbaru_SMC.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -582,21 +582,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2507069107</v>
+        <v>2506631917</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07 22:15:00</t>
+          <t>2026-09-07 21:05:55</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08 00:55:29</t>
+          <t>2026-09-07 21:43:41</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2j 40m</t>
+          <t>37m 46d</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -613,31 +613,31 @@
         <v>0.01</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>4414.713</v>
+        <v>4406.011</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>4418.713</v>
+        <v>4410.267</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>4408.713</v>
+        <v>4399.967</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>4408.713</v>
+        <v>4410.267</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>60</v>
+        <v>-42.6</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>6</v>
+        <v>-4.26</v>
       </c>
       <c r="O2" s="4" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
       <c r="P2" s="4" t="inlineStr">
         <is>
-          <t>Hit Take Profit (TP)</t>
+          <t>Hit Stop Loss (SL)</t>
         </is>
       </c>
       <c r="Q2" s="4" t="inlineStr">
@@ -651,21 +651,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2508904300</v>
+        <v>2507069107</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08 09:30:00</t>
+          <t>2026-09-07 22:15:00</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08 10:19:15</t>
+          <t>2026-09-08 00:55:29</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>49m 15d</t>
+          <t>2j 40m</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -675,29 +675,29 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="H3" s="4" t="n">
         <v>0.01</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>4425.155</v>
+        <v>4414.713</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>4419.63</v>
+        <v>4418.713</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>4433.63</v>
+        <v>4408.713</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>4433.63</v>
+        <v>4408.713</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>84.8</v>
+        <v>60</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>8.470000000000001</v>
+        <v>6</v>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
@@ -720,21 +720,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2512503275</v>
+        <v>2508904300</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08 20:14:59</t>
+          <t>2026-09-08 09:30:00</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08 20:29:36</t>
+          <t>2026-09-08 10:19:15</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>14m 37d</t>
+          <t>49m 15d</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -744,41 +744,179 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
         <v>0.01</v>
       </c>
       <c r="I4" s="4" t="n">
+        <v>4425.155</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>4419.63</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>4433.63</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>4433.63</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>Hit Take Profit (TP)</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM SMC/ICT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>2512503275</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08 20:14:59</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08 20:29:36</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>14m 37d</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I5" s="4" t="n">
         <v>4408.495</v>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="J5" s="4" t="n">
         <v>4414.695</v>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="K5" s="4" t="n">
         <v>4399.195</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L5" s="3" t="n">
         <v>4399.195</v>
       </c>
-      <c r="M4" s="4" t="n">
+      <c r="M5" s="4" t="n">
         <v>93</v>
       </c>
-      <c r="N4" s="3" t="n">
+      <c r="N5" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>Hit Take Profit (TP)</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM SMC/ICT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>2518131666</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09 17:44:20</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09 17:48:54</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>4m 34d</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>4395.151</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>4399.151</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>4389.151</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>4399.151</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>-40</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>LightGBM SMC/ICT</t>
         </is>
@@ -870,7 +1008,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>3 Trade</t>
+          <t>5 Trade</t>
         </is>
       </c>
     </row>
@@ -882,7 +1020,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
     </row>
@@ -906,7 +1044,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>0 Trade</t>
+          <t>2 Trade</t>
         </is>
       </c>
     </row>
@@ -918,7 +1056,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>60.00%</t>
         </is>
       </c>
     </row>
@@ -930,7 +1068,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>$+23.77 USD</t>
+          <t>$+15.51 USD</t>
         </is>
       </c>
     </row>
@@ -942,7 +1080,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>$+7.92 USD</t>
+          <t>$+3.10 USD</t>
         </is>
       </c>
     </row>
@@ -954,7 +1092,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Maksimal (100% Win, 0 Loss)</t>
+          <t>2.88</t>
         </is>
       </c>
     </row>
@@ -966,7 +1104,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 13:45:00 WIB</t>
+          <t>2026-09-09 17:55:32 WIB</t>
         </is>
       </c>
     </row>

--- a/Laporan_Forward_Testing_Model_Terbaru_SMC.xlsx
+++ b/Laporan_Forward_Testing_Model_Terbaru_SMC.xlsx
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 17:55:32 WIB</t>
+          <t>2026-09-09 18:06:48 WIB</t>
         </is>
       </c>
     </row>

--- a/Laporan_Forward_Testing_Model_Terbaru_SMC.xlsx
+++ b/Laporan_Forward_Testing_Model_Terbaru_SMC.xlsx
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 18:06:48 WIB</t>
+          <t>2026-09-09 18:42:53 WIB</t>
         </is>
       </c>
     </row>

--- a/Laporan_Forward_Testing_Model_Terbaru_SMC.xlsx
+++ b/Laporan_Forward_Testing_Model_Terbaru_SMC.xlsx
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-09 18:42:53 WIB</t>
+          <t>2026-09-10 01:58:10 WIB</t>
         </is>
       </c>
     </row>

--- a/Laporan_Forward_Testing_Model_Terbaru_SMC.xlsx
+++ b/Laporan_Forward_Testing_Model_Terbaru_SMC.xlsx
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 01:58:10 WIB</t>
+          <t>2026-09-10 02:09:27 WIB</t>
         </is>
       </c>
     </row>

--- a/Laporan_Forward_Testing_Model_Terbaru_SMC.xlsx
+++ b/Laporan_Forward_Testing_Model_Terbaru_SMC.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
@@ -487,7 +487,7 @@
     <col width="17" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="27" customWidth="1" min="16" max="16"/>
-    <col width="19" customWidth="1" min="17" max="17"/>
+    <col width="33" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -642,7 +642,7 @@
       </c>
       <c r="Q2" s="4" t="inlineStr">
         <is>
-          <t>LightGBM SMC/ICT</t>
+          <t>LightGBM M15 v3.4 (Confluence)</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>LightGBM SMC/ICT</t>
+          <t>LightGBM M15 v3.4 (Confluence)</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="Q4" s="4" t="inlineStr">
         <is>
-          <t>LightGBM SMC/ICT</t>
+          <t>LightGBM M15 v3.4 (Confluence)</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>LightGBM SMC/ICT</t>
+          <t>LightGBM M15 v3.4 (Confluence)</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,214 @@
       </c>
       <c r="Q6" s="4" t="inlineStr">
         <is>
-          <t>LightGBM SMC/ICT</t>
+          <t>LightGBM M15 v3.4 (Confluence)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>2528352257</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10 21:44:55</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10 22:02:27</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>17m 32d</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>4356.418</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>4367.036</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>4341.536</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>4354.983</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>Bot Trailing Profit Lock</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v3.4 (Confluence)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>2529630852</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11 01:44:54</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11 01:52:03</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>7m 9d</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>4334.166999999999</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>4329.411</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>4340.211</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>4335.417</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>Bot Trailing Profit Lock</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v3.4 (Confluence)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>2530715929</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11 08:14:55</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11 08:16:18</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>1m 23d</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>4333.135</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>4336.135</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>4328.635</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>4336.135</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>-30</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v3.4 (Confluence)</t>
         </is>
       </c>
     </row>
@@ -937,7 +1144,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="51" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -960,7 +1167,7 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>LightGBM SMC/ICT (28 Fitur SMC/ICT + DXY + MTF)</t>
+          <t>LightGBM M15 v3.4 (Confluence) (28 Fitur SMC/ICT + DXY + MTF)</t>
         </is>
       </c>
     </row>
@@ -984,7 +1191,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>&gt;= 60.0% + Trend Guard H1</t>
+          <t>Technical Confluence (Stoch RSI + Patterns v3.4)</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1215,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>5 Trade</t>
+          <t>8 Trade</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1227,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>8.0%</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1239,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>3 Trade</t>
+          <t>5 Trade</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1251,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>2 Trade</t>
+          <t>3 Trade</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1263,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>60.00%</t>
+          <t>62.50%</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1275,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>$+15.51 USD</t>
+          <t>$+15.20 USD</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1287,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>$+3.10 USD</t>
+          <t>$+1.90 USD</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1299,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.35</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1311,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 02:09:27 WIB</t>
+          <t>2026-09-11 17:08:27 WIB</t>
         </is>
       </c>
     </row>

--- a/Laporan_Forward_Testing_Model_Terbaru_SMC.xlsx
+++ b/Laporan_Forward_Testing_Model_Terbaru_SMC.xlsx
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 17:08:27 WIB</t>
+          <t>2026-09-11 17:09:27 WIB</t>
         </is>
       </c>
     </row>

--- a/Laporan_Forward_Testing_Model_Terbaru_SMC.xlsx
+++ b/Laporan_Forward_Testing_Model_Terbaru_SMC.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1129,6 +1129,144 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>2533679444</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11 17:59:54</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11 18:03:18</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>3m 24d</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>4337.891000000001</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>4341.154</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>4332.854</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>4341.154</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>-32.6</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-3.26</v>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v3.4 (Confluence)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>2534052853</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11 19:14:54</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11 19:17:58</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>3m 4d</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>4327.845</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>4324.545</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>4332.845</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>4332.845</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>Hit Take Profit (TP)</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v3.4 (Confluence)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1215,7 +1353,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>8 Trade</t>
+          <t>10 Trade</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1365,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1377,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>5 Trade</t>
+          <t>6 Trade</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1389,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>3 Trade</t>
+          <t>4 Trade</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1401,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>62.50%</t>
+          <t>60.00%</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1413,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>$+15.20 USD</t>
+          <t>$+16.94 USD</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1425,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>$+1.90 USD</t>
+          <t>$+1.69 USD</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1437,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.17</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1449,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 17:09:27 WIB</t>
+          <t>2026-09-11 21:16:23 WIB</t>
         </is>
       </c>
     </row>

--- a/Laporan_Forward_Testing_Model_Terbaru_SMC.xlsx
+++ b/Laporan_Forward_Testing_Model_Terbaru_SMC.xlsx
@@ -487,7 +487,7 @@
     <col width="17" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="27" customWidth="1" min="16" max="16"/>
-    <col width="33" customWidth="1" min="17" max="17"/>
+    <col width="34" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -642,7 +642,7 @@
       </c>
       <c r="Q2" s="4" t="inlineStr">
         <is>
-          <t>LightGBM M15 v3.4 (Confluence)</t>
+          <t>LightGBM M15 v3.5 (Macro + ATR)</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>LightGBM M15 v3.4 (Confluence)</t>
+          <t>LightGBM M15 v3.5 (Macro + ATR)</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="Q4" s="4" t="inlineStr">
         <is>
-          <t>LightGBM M15 v3.4 (Confluence)</t>
+          <t>LightGBM M15 v3.5 (Macro + ATR)</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>LightGBM M15 v3.4 (Confluence)</t>
+          <t>LightGBM M15 v3.5 (Macro + ATR)</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="Q6" s="4" t="inlineStr">
         <is>
-          <t>LightGBM M15 v3.4 (Confluence)</t>
+          <t>LightGBM M15 v3.5 (Macro + ATR)</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>LightGBM M15 v3.4 (Confluence)</t>
+          <t>LightGBM M15 v3.5 (Macro + ATR)</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t>LightGBM M15 v3.4 (Confluence)</t>
+          <t>LightGBM M15 v3.5 (Macro + ATR)</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>LightGBM M15 v3.4 (Confluence)</t>
+          <t>LightGBM M15 v3.5 (Macro + ATR)</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>LightGBM M15 v3.4 (Confluence)</t>
+          <t>LightGBM M15 v3.5 (Macro + ATR)</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>LightGBM M15 v3.4 (Confluence)</t>
+          <t>LightGBM M15 v3.5 (Macro + ATR)</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="65" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>LightGBM M15 v3.4 (Confluence) (28 Fitur SMC/ICT + DXY + MTF)</t>
+          <t>LightGBM M15 v3.5 (Macro + ATR) (28 Fitur SMC/ICT + DXY + MTF)</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Technical Confluence (Stoch RSI + Patterns v3.4)</t>
+          <t>Macro Calendar Guard + Dynamic ATR v3.5</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11 21:16:23 WIB</t>
+          <t>2026-09-14 13:55:14 WIB</t>
         </is>
       </c>
     </row>

--- a/Laporan_Forward_Testing_Model_Terbaru_SMC.xlsx
+++ b/Laporan_Forward_Testing_Model_Terbaru_SMC.xlsx
@@ -7,8 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Log Model Terbaru" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan Statistik" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Log Model Terbaru (v3.7)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan Statistik (v3.7)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Log Model Terbaru (v3.6)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan Statistik (v3.6)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Log M15 (Arsip v3.5)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan Statistik (v3.5)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Log M15 (Arsip 16-17 Sep)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan Statistik (Arsip 16-1" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -41,7 +47,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -52,6 +58,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
         <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -87,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -102,6 +120,26 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -468,7 +506,1207 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:R3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="17" max="17"/>
+    <col width="50" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Trade Ke-</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Ticket Posisi</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Waktu Open</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Waktu Close</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Durasi</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Simbol</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>Harga Entry</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>Take Profit (TP)</t>
+        </is>
+      </c>
+      <c r="L1" s="7" t="inlineStr">
+        <is>
+          <t>Harga Exit</t>
+        </is>
+      </c>
+      <c r="M1" s="7" t="inlineStr">
+        <is>
+          <t>Pips (P/L)</t>
+        </is>
+      </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t>Profit ($ USD)</t>
+        </is>
+      </c>
+      <c r="O1" s="7" t="inlineStr">
+        <is>
+          <t>Saldo ($ USD)</t>
+        </is>
+      </c>
+      <c r="P1" s="7" t="inlineStr">
+        <is>
+          <t>Hasil</t>
+        </is>
+      </c>
+      <c r="Q1" s="7" t="inlineStr">
+        <is>
+          <t>Keterangan / Alasan Exit</t>
+        </is>
+      </c>
+      <c r="R1" s="7" t="inlineStr">
+        <is>
+          <t>Model AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="12" t="n">
+        <v>2573313197</v>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-18 22:14:55</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-18 22:38:46</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>23m 51d</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H2" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I2" s="14" t="n">
+        <v>4352.281</v>
+      </c>
+      <c r="J2" s="14" t="n">
+        <v>4345.281</v>
+      </c>
+      <c r="K2" s="14" t="n">
+        <v>4369.781</v>
+      </c>
+      <c r="L2" s="14" t="n">
+        <v>4352.481</v>
+      </c>
+      <c r="M2" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N2" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O2" s="12" t="n">
+        <v>500.2</v>
+      </c>
+      <c r="P2" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q2" s="13" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R2" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v3.7 (Wide SL + RRR 2.5 + Sniper)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12" t="n">
+        <v>2573549087</v>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-18 22:59:55</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-18 23:29:18</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>29m 23d</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I3" s="14" t="n">
+        <v>4356.893</v>
+      </c>
+      <c r="J3" s="14" t="n">
+        <v>4349.893</v>
+      </c>
+      <c r="K3" s="14" t="n">
+        <v>4374.393</v>
+      </c>
+      <c r="L3" s="14" t="n">
+        <v>4374.393</v>
+      </c>
+      <c r="M3" s="12" t="n">
+        <v>175</v>
+      </c>
+      <c r="N3" s="14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="O3" s="12" t="n">
+        <v>517.7</v>
+      </c>
+      <c r="P3" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q3" s="13" t="inlineStr">
+        <is>
+          <t>Hit Take Profit (TP)</t>
+        </is>
+      </c>
+      <c r="R3" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v3.7 (Wide SL + RRR 2.5 + Sniper)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="81" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Metrik Evaluasi Forward Testing</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Nilai Evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Nama Model</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v3.7 (Wide SL + RRR 2.5 + Sniper) (28 Fitur SMC/ICT + DXY + MTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Metode Eksekusi</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Otomatis 0-Delay (MetaTrader 5 API)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Ambang Batas Keyakinan (Threshold)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Versi 3.7 (Wide SL + RRR 2.5 + Sniper Entry)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Target Forward Testing Skripsi</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>100 Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Saldo Awal Evaluasi</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>$500.00 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Saldo Terkini</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>$517.70 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Total Trade Otomatis Selesai</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>2 Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Progres Evaluasi (%)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>2.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Jumlah Trade WIN (Profit)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>2 Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Jumlah Trade LOSS (Rugi)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>0 Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Win Rate (%)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Total Akumulasi Profit ($ USD)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>$+17.70 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Return on Investment (ROI)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>+3.54%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Rata-rata Profit per Trade</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>$+8.85 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Maksimal (100% Win, 0 Loss)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Waktu Pembaruan Terakhir</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:19:27 WIB</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="17" max="17"/>
+    <col width="50" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Trade Ke-</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Ticket Posisi</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Waktu Open</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Waktu Close</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Durasi</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Simbol</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>Harga Entry</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>Take Profit (TP)</t>
+        </is>
+      </c>
+      <c r="L1" s="7" t="inlineStr">
+        <is>
+          <t>Harga Exit</t>
+        </is>
+      </c>
+      <c r="M1" s="7" t="inlineStr">
+        <is>
+          <t>Pips (P/L)</t>
+        </is>
+      </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t>Profit ($ USD)</t>
+        </is>
+      </c>
+      <c r="O1" s="7" t="inlineStr">
+        <is>
+          <t>Saldo ($ USD)</t>
+        </is>
+      </c>
+      <c r="P1" s="7" t="inlineStr">
+        <is>
+          <t>Hasil</t>
+        </is>
+      </c>
+      <c r="Q1" s="7" t="inlineStr">
+        <is>
+          <t>Keterangan / Alasan Exit</t>
+        </is>
+      </c>
+      <c r="R1" s="7" t="inlineStr">
+        <is>
+          <t>Model AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="n">
+        <v>2549455494</v>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-15 14:59:54</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-15 15:00:14</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>0m 20d</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H2" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I2" s="11" t="n">
+        <v>4280.733999999999</v>
+      </c>
+      <c r="J2" s="11" t="n">
+        <v>4277.334</v>
+      </c>
+      <c r="K2" s="11" t="n">
+        <v>4285.834</v>
+      </c>
+      <c r="L2" s="11" t="n">
+        <v>4277.334</v>
+      </c>
+      <c r="M2" s="9" t="n">
+        <v>-34</v>
+      </c>
+      <c r="N2" s="11" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="O2" s="9" t="n">
+        <v>496.6</v>
+      </c>
+      <c r="P2" s="9" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="Q2" s="10" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R2" s="10" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v3.7 (Wide SL + RRR 2.5 + Sniper)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12" t="n">
+        <v>2550031186</v>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-15 16:29:54</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-15 16:41:54</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>12m 0d</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I3" s="14" t="n">
+        <v>4267.536</v>
+      </c>
+      <c r="J3" s="14" t="n">
+        <v>4264.036</v>
+      </c>
+      <c r="K3" s="14" t="n">
+        <v>4272.736</v>
+      </c>
+      <c r="L3" s="14" t="n">
+        <v>4269.886</v>
+      </c>
+      <c r="M3" s="12" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="N3" s="14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O3" s="12" t="n">
+        <v>498.95</v>
+      </c>
+      <c r="P3" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q3" s="13" t="inlineStr">
+        <is>
+          <t>Bot Trailing Profit Lock</t>
+        </is>
+      </c>
+      <c r="R3" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v3.7 (Wide SL + RRR 2.5 + Sniper)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>2550255645</v>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:14:54</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:36:21</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>21m 27d</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I4" s="11" t="n">
+        <v>4273.069</v>
+      </c>
+      <c r="J4" s="11" t="n">
+        <v>4276.453</v>
+      </c>
+      <c r="K4" s="11" t="n">
+        <v>4267.753</v>
+      </c>
+      <c r="L4" s="11" t="n">
+        <v>4276.453</v>
+      </c>
+      <c r="M4" s="9" t="n">
+        <v>-33.8</v>
+      </c>
+      <c r="N4" s="11" t="n">
+        <v>-3.38</v>
+      </c>
+      <c r="O4" s="9" t="n">
+        <v>495.57</v>
+      </c>
+      <c r="P4" s="9" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="Q4" s="10" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R4" s="10" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v3.7 (Wide SL + RRR 2.5 + Sniper)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>2550821039</v>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-15 19:14:54</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-15 19:17:53</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>2m 59d</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>4278.594</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>4281.594</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>4274.094</v>
+      </c>
+      <c r="L5" s="14" t="n">
+        <v>4274.094</v>
+      </c>
+      <c r="M5" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="N5" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O5" s="12" t="n">
+        <v>500.07</v>
+      </c>
+      <c r="P5" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q5" s="13" t="inlineStr">
+        <is>
+          <t>Hit Take Profit (TP)</t>
+        </is>
+      </c>
+      <c r="R5" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v3.7 (Wide SL + RRR 2.5 + Sniper)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>2550905093</v>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-15 19:29:53</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-15 19:34:18</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>4m 25d</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>4277.193</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>4280.193</v>
+      </c>
+      <c r="K6" s="11" t="n">
+        <v>4272.693</v>
+      </c>
+      <c r="L6" s="11" t="n">
+        <v>4280.193</v>
+      </c>
+      <c r="M6" s="9" t="n">
+        <v>-30</v>
+      </c>
+      <c r="N6" s="11" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O6" s="9" t="n">
+        <v>497.07</v>
+      </c>
+      <c r="P6" s="9" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="Q6" s="10" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R6" s="10" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v3.7 (Wide SL + RRR 2.5 + Sniper)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="81" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Metrik Evaluasi Forward Testing</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Nilai Evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Nama Model</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v3.7 (Wide SL + RRR 2.5 + Sniper) (28 Fitur SMC/ICT + DXY + MTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Metode Eksekusi</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Otomatis 0-Delay (MetaTrader 5 API)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Ambang Batas Keyakinan (Threshold)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Versi 3.7 (Wide SL + RRR 2.5 + Sniper Entry)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Target Forward Testing Skripsi</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>100 Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Saldo Awal Evaluasi</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>$500.00 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Saldo Terkini</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>$497.07 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Total Trade Otomatis Selesai</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>5 Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Progres Evaluasi (%)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>5.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Jumlah Trade WIN (Profit)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>2 Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Jumlah Trade LOSS (Rugi)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>3 Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Win Rate (%)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>40.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Total Akumulasi Profit ($ USD)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>$-2.93 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Return on Investment (ROI)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>-0.59%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Rata-rata Profit per Trade</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>$-0.59 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Waktu Pembaruan Terakhir</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:16:18 WIB</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1267,12 +2505,288 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>2543863976</v>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14 19:29:54</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14 19:35:03</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>5m 9d</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>4286.315000000001</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>4289.815</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>4281.115</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>4289.815</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>-35</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v3.5 (Macro + ATR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>2544734882</v>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14 20:44:54</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14 20:45:15</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>0m 21d</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>4273.519</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>4276.856</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>4268.156</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>4276.856</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>-33.4</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>-3.34</v>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v3.5 (Macro + ATR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>2544885437</v>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14 20:59:54</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14 21:03:26</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>3m 32d</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>4272.742</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>4276.242</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>4267.542</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>4267.542</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="P14" s="4" t="inlineStr">
+        <is>
+          <t>Hit Take Profit (TP)</t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v3.5 (Macro + ATR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>2545951914</v>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:59:55</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14 23:07:57</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>8m 2d</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>4288.264</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>4291.764</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>4283.064</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>4291.764</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>-35</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v3.5 (Macro + ATR)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1353,7 +2867,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>10 Trade</t>
+          <t>14 Trade</t>
         </is>
       </c>
     </row>
@@ -1365,7 +2879,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>14.0%</t>
         </is>
       </c>
     </row>
@@ -1377,7 +2891,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>6 Trade</t>
+          <t>7 Trade</t>
         </is>
       </c>
     </row>
@@ -1389,7 +2903,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>4 Trade</t>
+          <t>7 Trade</t>
         </is>
       </c>
     </row>
@@ -1401,7 +2915,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>60.00%</t>
+          <t>50.00%</t>
         </is>
       </c>
     </row>
@@ -1413,7 +2927,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>$+16.94 USD</t>
+          <t>$+11.80 USD</t>
         </is>
       </c>
     </row>
@@ -1425,7 +2939,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>$+1.69 USD</t>
+          <t>$+0.84 USD</t>
         </is>
       </c>
     </row>
@@ -1437,7 +2951,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
@@ -1449,7 +2963,787 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14 13:55:14 WIB</t>
+          <t>2026-09-15 00:41:10 WIB</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="17" max="17"/>
+    <col width="50" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Trade Ke-</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Ticket Posisi</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Waktu Open</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Waktu Close</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Durasi</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Simbol</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>Harga Entry</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>Take Profit (TP)</t>
+        </is>
+      </c>
+      <c r="L1" s="7" t="inlineStr">
+        <is>
+          <t>Harga Exit</t>
+        </is>
+      </c>
+      <c r="M1" s="7" t="inlineStr">
+        <is>
+          <t>Pips (P/L)</t>
+        </is>
+      </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t>Profit ($ USD)</t>
+        </is>
+      </c>
+      <c r="O1" s="7" t="inlineStr">
+        <is>
+          <t>Saldo ($ USD)</t>
+        </is>
+      </c>
+      <c r="P1" s="7" t="inlineStr">
+        <is>
+          <t>Hasil</t>
+        </is>
+      </c>
+      <c r="Q1" s="7" t="inlineStr">
+        <is>
+          <t>Keterangan / Alasan Exit</t>
+        </is>
+      </c>
+      <c r="R1" s="7" t="inlineStr">
+        <is>
+          <t>Model AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="12" t="n">
+        <v>2553364900</v>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-16 01:59:55</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-16 03:27:41</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>1j 27m</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="H2" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I2" s="14" t="n">
+        <v>4308.455</v>
+      </c>
+      <c r="J2" s="14" t="n">
+        <v>4314.155</v>
+      </c>
+      <c r="K2" s="14" t="n">
+        <v>4294.255</v>
+      </c>
+      <c r="L2" s="14" t="n">
+        <v>4294.255</v>
+      </c>
+      <c r="M2" s="12" t="n">
+        <v>142</v>
+      </c>
+      <c r="N2" s="14" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="O2" s="12" t="n">
+        <v>514.2</v>
+      </c>
+      <c r="P2" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q2" s="13" t="inlineStr">
+        <is>
+          <t>Hit Take Profit (TP)</t>
+        </is>
+      </c>
+      <c r="R2" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v3.7 (Wide SL + RRR 2.5 + Sniper)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12" t="n">
+        <v>2557900161</v>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-16 20:29:55</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-16 20:56:06</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>26m 11d</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I3" s="14" t="n">
+        <v>4352.512</v>
+      </c>
+      <c r="J3" s="14" t="n">
+        <v>4359.112</v>
+      </c>
+      <c r="K3" s="14" t="n">
+        <v>4336.012</v>
+      </c>
+      <c r="L3" s="14" t="n">
+        <v>4336.012</v>
+      </c>
+      <c r="M3" s="12" t="n">
+        <v>165</v>
+      </c>
+      <c r="N3" s="14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="O3" s="12" t="n">
+        <v>530.7</v>
+      </c>
+      <c r="P3" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q3" s="13" t="inlineStr">
+        <is>
+          <t>Hit Take Profit (TP)</t>
+        </is>
+      </c>
+      <c r="R3" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v3.7 (Wide SL + RRR 2.5 + Sniper)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="12" t="n">
+        <v>2561281921</v>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-17 02:44:54</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-17 02:46:49</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>1m 55d</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I4" s="14" t="n">
+        <v>4266.42</v>
+      </c>
+      <c r="J4" s="14" t="n">
+        <v>4260.42</v>
+      </c>
+      <c r="K4" s="14" t="n">
+        <v>4278.42</v>
+      </c>
+      <c r="L4" s="14" t="n">
+        <v>4266.62</v>
+      </c>
+      <c r="M4" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O4" s="12" t="n">
+        <v>530.9</v>
+      </c>
+      <c r="P4" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q4" s="13" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R4" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v3.7 (Wide SL + RRR 2.5 + Sniper)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>2564213216</v>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-17 15:14:54</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:27:43</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>1j 12m</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>4320.186</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>4326.186</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>4308.186</v>
+      </c>
+      <c r="L5" s="14" t="n">
+        <v>4308.186</v>
+      </c>
+      <c r="M5" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="N5" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="O5" s="12" t="n">
+        <v>542.9</v>
+      </c>
+      <c r="P5" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q5" s="13" t="inlineStr">
+        <is>
+          <t>Hit Take Profit (TP)</t>
+        </is>
+      </c>
+      <c r="R5" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v3.7 (Wide SL + RRR 2.5 + Sniper)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>2566662919</v>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-17 21:14:54</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-17 21:15:40</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>0m 46d</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>4371.472</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>4364.593</v>
+      </c>
+      <c r="K6" s="11" t="n">
+        <v>4382.093</v>
+      </c>
+      <c r="L6" s="11" t="n">
+        <v>4370.278</v>
+      </c>
+      <c r="M6" s="9" t="n">
+        <v>-11.9</v>
+      </c>
+      <c r="N6" s="11" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="O6" s="9" t="n">
+        <v>541.71</v>
+      </c>
+      <c r="P6" s="9" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="Q6" s="10" t="inlineStr">
+        <is>
+          <t>M15 v3.6 Z-C</t>
+        </is>
+      </c>
+      <c r="R6" s="10" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v3.7 (Wide SL + RRR 2.5 + Sniper)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>2567361135</v>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-17 22:59:54</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-17 23:26:12</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>26m 18d</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>4369.779</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>4363.852</v>
+      </c>
+      <c r="K7" s="11" t="n">
+        <v>4381.852</v>
+      </c>
+      <c r="L7" s="11" t="n">
+        <v>4363.852</v>
+      </c>
+      <c r="M7" s="9" t="n">
+        <v>-59.3</v>
+      </c>
+      <c r="N7" s="11" t="n">
+        <v>-5.93</v>
+      </c>
+      <c r="O7" s="9" t="n">
+        <v>535.78</v>
+      </c>
+      <c r="P7" s="9" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="Q7" s="10" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R7" s="10" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v3.7 (Wide SL + RRR 2.5 + Sniper)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="81" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Metrik Evaluasi Forward Testing</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Nilai Evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Nama Model</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v3.7 (Wide SL + RRR 2.5 + Sniper) (28 Fitur SMC/ICT + DXY + MTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Metode Eksekusi</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Otomatis 0-Delay (MetaTrader 5 API)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Ambang Batas Keyakinan (Threshold)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Versi 3.7 (Wide SL + RRR 2.5 + Sniper Entry)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Target Forward Testing Skripsi</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>100 Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Saldo Awal Evaluasi</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>$500.00 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Saldo Terkini</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>$535.78 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Total Trade Otomatis Selesai</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>6 Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Progres Evaluasi (%)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>6.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Jumlah Trade WIN (Profit)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>4 Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Jumlah Trade LOSS (Rugi)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>2 Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Win Rate (%)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>66.67%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Total Akumulasi Profit ($ USD)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>$+35.78 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Return on Investment (ROI)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>+7.16%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Rata-rata Profit per Trade</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>$+5.96 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>6.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Waktu Pembaruan Terakhir</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-17 23:54:14 WIB</t>
         </is>
       </c>
     </row>

--- a/Laporan_Forward_Testing_Model_Terbaru_SMC.xlsx
+++ b/Laporan_Forward_Testing_Model_Terbaru_SMC.xlsx
@@ -983,7 +983,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19 00:19:27 WIB</t>
+          <t>2026-09-19 00:54:55 WIB</t>
         </is>
       </c>
     </row>

--- a/Laporan_Forward_Testing_Model_Terbaru_SMC.xlsx
+++ b/Laporan_Forward_Testing_Model_Terbaru_SMC.xlsx
@@ -4,17 +4,19 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Log Model Terbaru (v3.7)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan Statistik (v3.7)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Log Model Terbaru (v3.6)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan Statistik (v3.6)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Log M15 (Arsip v3.5)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan Statistik (v3.5)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Log M15 (Arsip 16-17 Sep)" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan Statistik (Arsip 16-1" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Log Model Terbaru (v4.1)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan Statistik (v4.1)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Log Model Terbaru (v3.6)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan Statistik (v3.6)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Log M15 (Arsip v3.5)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan Statistik (v3.5)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Log M15 (Arsip 16-17 Sep)" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan Statistik (Arsip 16-1" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -506,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -517,7 +519,7 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -526,7 +528,7 @@
     <col width="17" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="28" customWidth="1" min="17" max="17"/>
-    <col width="50" customWidth="1" min="18" max="18"/>
+    <col width="48" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -689,7 +691,7 @@
       </c>
       <c r="R2" s="13" t="inlineStr">
         <is>
-          <t>LightGBM M15 v3.7 (Wide SL + RRR 2.5 + Sniper)</t>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
         </is>
       </c>
     </row>
@@ -761,7 +763,1597 @@
       </c>
       <c r="R3" s="13" t="inlineStr">
         <is>
-          <t>LightGBM M15 v3.7 (Wide SL + RRR 2.5 + Sniper)</t>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>2577450981</v>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-21 07:44:54</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-21 07:51:02</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>6m 8d</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I4" s="11" t="n">
+        <v>4368.619</v>
+      </c>
+      <c r="J4" s="11" t="n">
+        <v>4363.431</v>
+      </c>
+      <c r="K4" s="11" t="n">
+        <v>4380.931</v>
+      </c>
+      <c r="L4" s="11" t="n">
+        <v>4362.783</v>
+      </c>
+      <c r="M4" s="9" t="n">
+        <v>-58.4</v>
+      </c>
+      <c r="N4" s="11" t="n">
+        <v>-5.84</v>
+      </c>
+      <c r="O4" s="9" t="n">
+        <v>511.86</v>
+      </c>
+      <c r="P4" s="9" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="Q4" s="10" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R4" s="10" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>2579837091</v>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:44:54</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:54:56</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>10m 2d</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>4357.664</v>
+      </c>
+      <c r="J5" s="11" t="n">
+        <v>4351.264</v>
+      </c>
+      <c r="K5" s="11" t="n">
+        <v>4373.664</v>
+      </c>
+      <c r="L5" s="11" t="n">
+        <v>4351.264</v>
+      </c>
+      <c r="M5" s="9" t="n">
+        <v>-64</v>
+      </c>
+      <c r="N5" s="11" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="O5" s="9" t="n">
+        <v>505.46</v>
+      </c>
+      <c r="P5" s="9" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="Q5" s="10" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R5" s="10" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>2583401048</v>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-22 03:29:55</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-22 05:08:10</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>1j 38m</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I6" s="14" t="n">
+        <v>4340.675</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>4336.175</v>
+      </c>
+      <c r="K6" s="14" t="n">
+        <v>4349.675</v>
+      </c>
+      <c r="L6" s="14" t="n">
+        <v>4349.675</v>
+      </c>
+      <c r="M6" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="N6" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="O6" s="12" t="n">
+        <v>514.46</v>
+      </c>
+      <c r="P6" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q6" s="13" t="inlineStr">
+        <is>
+          <t>Hit Take Profit (TP)</t>
+        </is>
+      </c>
+      <c r="R6" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>2584927512</v>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:14:55</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:19:50</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>1j 4m</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>4339.094</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>4332.394</v>
+      </c>
+      <c r="K7" s="14" t="n">
+        <v>4355.894</v>
+      </c>
+      <c r="L7" s="14" t="n">
+        <v>4339.294</v>
+      </c>
+      <c r="M7" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N7" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O7" s="12" t="n">
+        <v>514.66</v>
+      </c>
+      <c r="P7" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q7" s="13" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R7" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>2585747588</v>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-22 13:59:55</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-22 14:28:34</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>28m 39d</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>4318.927</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>4311.927</v>
+      </c>
+      <c r="K8" s="14" t="n">
+        <v>4336.427</v>
+      </c>
+      <c r="L8" s="14" t="n">
+        <v>4319.127</v>
+      </c>
+      <c r="M8" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O8" s="12" t="n">
+        <v>514.86</v>
+      </c>
+      <c r="P8" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q8" s="13" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R8" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>2587188646</v>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-22 17:59:55</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-22 18:55:35</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>55m 40d</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>4322.68</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>4329.969</v>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>4305.469</v>
+      </c>
+      <c r="L9" s="14" t="n">
+        <v>4322.48</v>
+      </c>
+      <c r="M9" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O9" s="12" t="n">
+        <v>515.0599999999999</v>
+      </c>
+      <c r="P9" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q9" s="13" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R9" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>2591745453</v>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:29:55</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23 15:10:44</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>40m 49d</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>4324.741</v>
+      </c>
+      <c r="J10" s="11" t="n">
+        <v>4317.487</v>
+      </c>
+      <c r="K10" s="11" t="n">
+        <v>4342.687</v>
+      </c>
+      <c r="L10" s="11" t="n">
+        <v>4317.487</v>
+      </c>
+      <c r="M10" s="9" t="n">
+        <v>-72.5</v>
+      </c>
+      <c r="N10" s="11" t="n">
+        <v>-7.25</v>
+      </c>
+      <c r="O10" s="9" t="n">
+        <v>507.81</v>
+      </c>
+      <c r="P10" s="9" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="Q10" s="10" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R10" s="10" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>2592236187</v>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23 16:44:54</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23 16:48:34</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>3m 40d</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>4316.467</v>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>4309.667</v>
+      </c>
+      <c r="K11" s="11" t="n">
+        <v>4333.467</v>
+      </c>
+      <c r="L11" s="11" t="n">
+        <v>4309.667</v>
+      </c>
+      <c r="M11" s="9" t="n">
+        <v>-68</v>
+      </c>
+      <c r="N11" s="11" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="O11" s="9" t="n">
+        <v>501.01</v>
+      </c>
+      <c r="P11" s="9" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="Q11" s="10" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R11" s="10" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>2592746187</v>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-23 18:44:54</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-23 18:48:07</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>3m 13d</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>4304.452</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>4297.352</v>
+      </c>
+      <c r="K12" s="14" t="n">
+        <v>4322.252</v>
+      </c>
+      <c r="L12" s="14" t="n">
+        <v>4304.652</v>
+      </c>
+      <c r="M12" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O12" s="12" t="n">
+        <v>501.21</v>
+      </c>
+      <c r="P12" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q12" s="13" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R12" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>2592820420</v>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-23 18:59:55</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:30:14</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>30m 19d</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>4309.479</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>4303.079</v>
+      </c>
+      <c r="K13" s="14" t="n">
+        <v>4322.279</v>
+      </c>
+      <c r="L13" s="14" t="n">
+        <v>4309.679</v>
+      </c>
+      <c r="M13" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N13" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O13" s="12" t="n">
+        <v>501.41</v>
+      </c>
+      <c r="P13" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q13" s="13" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R13" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>2593179348</v>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:54</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23 20:08:03</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>8m 9d</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>4310.338</v>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>4302.738</v>
+      </c>
+      <c r="K14" s="11" t="n">
+        <v>4325.538</v>
+      </c>
+      <c r="L14" s="11" t="n">
+        <v>4302.738</v>
+      </c>
+      <c r="M14" s="9" t="n">
+        <v>-76</v>
+      </c>
+      <c r="N14" s="11" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="O14" s="9" t="n">
+        <v>493.81</v>
+      </c>
+      <c r="P14" s="9" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="Q14" s="10" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R14" s="10" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>2595301847</v>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-24 02:59:55</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-24 06:43:32</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>3j 43m</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I15" s="14" t="n">
+        <v>4284.755</v>
+      </c>
+      <c r="J15" s="14" t="n">
+        <v>4276.255</v>
+      </c>
+      <c r="K15" s="14" t="n">
+        <v>4305.955</v>
+      </c>
+      <c r="L15" s="14" t="n">
+        <v>4284.955</v>
+      </c>
+      <c r="M15" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N15" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O15" s="12" t="n">
+        <v>494.01</v>
+      </c>
+      <c r="P15" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q15" s="13" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R15" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>2596572850</v>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-24 11:14:55</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:31:55</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>1j 17m</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <v>4285.272</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>4276.772</v>
+      </c>
+      <c r="K16" s="14" t="n">
+        <v>4306.472</v>
+      </c>
+      <c r="L16" s="14" t="n">
+        <v>4285.472</v>
+      </c>
+      <c r="M16" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N16" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O16" s="12" t="n">
+        <v>494.21</v>
+      </c>
+      <c r="P16" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q16" s="13" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R16" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>2596946151</v>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:59:54</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:35:57</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>36m 3d</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>4279.52</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>4271.42</v>
+      </c>
+      <c r="K17" s="14" t="n">
+        <v>4299.72</v>
+      </c>
+      <c r="L17" s="14" t="n">
+        <v>4279.72</v>
+      </c>
+      <c r="M17" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N17" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O17" s="12" t="n">
+        <v>494.41</v>
+      </c>
+      <c r="P17" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q17" s="13" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R17" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="12" t="n">
+        <v>2597157735</v>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:44:55</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:50:04</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>1j 5m</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I18" s="14" t="n">
+        <v>4278.702</v>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>4271.302</v>
+      </c>
+      <c r="K18" s="14" t="n">
+        <v>4297.202</v>
+      </c>
+      <c r="L18" s="14" t="n">
+        <v>4278.902</v>
+      </c>
+      <c r="M18" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N18" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O18" s="12" t="n">
+        <v>494.61</v>
+      </c>
+      <c r="P18" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q18" s="13" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R18" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>2597949075</v>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:14:55</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:30:23</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>15m 28d</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>4263.299</v>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>4254.865</v>
+      </c>
+      <c r="K19" s="11" t="n">
+        <v>4284.565</v>
+      </c>
+      <c r="L19" s="11" t="n">
+        <v>4254.865</v>
+      </c>
+      <c r="M19" s="9" t="n">
+        <v>-84.3</v>
+      </c>
+      <c r="N19" s="11" t="n">
+        <v>-8.43</v>
+      </c>
+      <c r="O19" s="9" t="n">
+        <v>486.18</v>
+      </c>
+      <c r="P19" s="9" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="Q19" s="10" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R19" s="10" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="12" t="n">
+        <v>2598448052</v>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-24 17:44:54</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-24 17:51:29</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>6m 35d</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I20" s="14" t="n">
+        <v>4259.055</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>4251.492</v>
+      </c>
+      <c r="K20" s="14" t="n">
+        <v>4274.292</v>
+      </c>
+      <c r="L20" s="14" t="n">
+        <v>4259.255</v>
+      </c>
+      <c r="M20" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N20" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O20" s="12" t="n">
+        <v>486.38</v>
+      </c>
+      <c r="P20" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q20" s="13" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R20" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="12" t="n">
+        <v>2600157994</v>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-24 22:44:54</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-24 22:55:44</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>10m 50d</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>4255.261</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>4247.661</v>
+      </c>
+      <c r="K21" s="14" t="n">
+        <v>4270.461</v>
+      </c>
+      <c r="L21" s="14" t="n">
+        <v>4255.461</v>
+      </c>
+      <c r="M21" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N21" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O21" s="12" t="n">
+        <v>486.58</v>
+      </c>
+      <c r="P21" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q21" s="13" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R21" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="12" t="n">
+        <v>2600228870</v>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-24 22:59:54</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:16:17</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>16m 23d</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I22" s="14" t="n">
+        <v>4256.853</v>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>4249.253</v>
+      </c>
+      <c r="K22" s="14" t="n">
+        <v>4272.053</v>
+      </c>
+      <c r="L22" s="14" t="n">
+        <v>4272.053</v>
+      </c>
+      <c r="M22" s="12" t="n">
+        <v>152</v>
+      </c>
+      <c r="N22" s="14" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="O22" s="12" t="n">
+        <v>501.78</v>
+      </c>
+      <c r="P22" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q22" s="13" t="inlineStr">
+        <is>
+          <t>Hit Take Profit (TP)</t>
+        </is>
+      </c>
+      <c r="R22" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="81" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Metrik Evaluasi Forward Testing</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Nilai Evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Nama Model</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v3.7 (Wide SL + RRR 2.5 + Sniper) (28 Fitur SMC/ICT + DXY + MTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Metode Eksekusi</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Otomatis 0-Delay (MetaTrader 5 API)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Ambang Batas Keyakinan (Threshold)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Versi 3.7 (Wide SL + RRR 2.5 + Sniper Entry)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Target Forward Testing Skripsi</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>100 Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Saldo Awal Evaluasi</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>$500.00 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Saldo Terkini</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>$535.78 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Total Trade Otomatis Selesai</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>6 Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Progres Evaluasi (%)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>6.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Jumlah Trade WIN (Profit)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>4 Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Jumlah Trade LOSS (Rugi)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>2 Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Win Rate (%)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>66.67%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Total Akumulasi Profit ($ USD)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>$+35.78 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Return on Investment (ROI)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>+7.16%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Rata-rata Profit per Trade</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>$+5.96 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>6.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Waktu Pembaruan Terakhir</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-17 23:54:14 WIB</t>
         </is>
       </c>
     </row>
@@ -780,7 +2372,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="81" customWidth="1" min="2" max="2"/>
+    <col width="79" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -803,7 +2395,7 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>LightGBM M15 v3.7 (Wide SL + RRR 2.5 + Sniper) (28 Fitur SMC/ICT + DXY + MTF)</t>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF) (28 Fitur SMC/ICT + DXY + MTF)</t>
         </is>
       </c>
     </row>
@@ -827,7 +2419,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Versi 3.7 (Wide SL + RRR 2.5 + Sniper Entry)</t>
+          <t>Versi 4.1 (Structural RRR + Adaptive Hybrid)</t>
         </is>
       </c>
     </row>
@@ -863,7 +2455,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>$517.70 USD</t>
+          <t>$501.78 USD</t>
         </is>
       </c>
     </row>
@@ -875,7 +2467,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2 Trade</t>
+          <t>21 Trade</t>
         </is>
       </c>
     </row>
@@ -887,7 +2479,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>21.0%</t>
         </is>
       </c>
     </row>
@@ -899,7 +2491,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>2 Trade</t>
+          <t>15 Trade</t>
         </is>
       </c>
     </row>
@@ -911,7 +2503,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>0 Trade</t>
+          <t>6 Trade</t>
         </is>
       </c>
     </row>
@@ -923,7 +2515,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>71.43%</t>
         </is>
       </c>
     </row>
@@ -935,7 +2527,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>$+17.70 USD</t>
+          <t>$+1.78 USD</t>
         </is>
       </c>
     </row>
@@ -947,7 +2539,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>+3.54%</t>
+          <t>+0.36%</t>
         </is>
       </c>
     </row>
@@ -959,7 +2551,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>$+8.85 USD</t>
+          <t>$+0.08 USD</t>
         </is>
       </c>
     </row>
@@ -971,7 +2563,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Maksimal (100% Win, 0 Loss)</t>
+          <t>1.04</t>
         </is>
       </c>
     </row>
@@ -983,7 +2575,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19 00:54:55 WIB</t>
+          <t>2026-09-24 23:30:23 WIB</t>
         </is>
       </c>
     </row>
@@ -993,6 +2585,1938 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="17" max="17"/>
+    <col width="48" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Trade Ke-</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Ticket Posisi</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Waktu Open</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Waktu Close</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Durasi</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Simbol</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>Harga Entry</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>Take Profit (TP)</t>
+        </is>
+      </c>
+      <c r="L1" s="7" t="inlineStr">
+        <is>
+          <t>Harga Exit</t>
+        </is>
+      </c>
+      <c r="M1" s="7" t="inlineStr">
+        <is>
+          <t>Pips (P/L)</t>
+        </is>
+      </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t>Profit ($ USD)</t>
+        </is>
+      </c>
+      <c r="O1" s="7" t="inlineStr">
+        <is>
+          <t>Saldo ($ USD)</t>
+        </is>
+      </c>
+      <c r="P1" s="7" t="inlineStr">
+        <is>
+          <t>Hasil</t>
+        </is>
+      </c>
+      <c r="Q1" s="7" t="inlineStr">
+        <is>
+          <t>Keterangan / Alasan Exit</t>
+        </is>
+      </c>
+      <c r="R1" s="7" t="inlineStr">
+        <is>
+          <t>Model AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="12" t="n">
+        <v>2573313197</v>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-18 22:14:55</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-18 22:38:46</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>23m 51d</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H2" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I2" s="14" t="n">
+        <v>4352.281</v>
+      </c>
+      <c r="J2" s="14" t="n">
+        <v>4345.281</v>
+      </c>
+      <c r="K2" s="14" t="n">
+        <v>4369.781</v>
+      </c>
+      <c r="L2" s="14" t="n">
+        <v>4352.481</v>
+      </c>
+      <c r="M2" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N2" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O2" s="12" t="n">
+        <v>500.2</v>
+      </c>
+      <c r="P2" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q2" s="13" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R2" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12" t="n">
+        <v>2573549087</v>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-18 22:59:55</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-18 23:29:18</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>29m 23d</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I3" s="14" t="n">
+        <v>4356.893</v>
+      </c>
+      <c r="J3" s="14" t="n">
+        <v>4349.893</v>
+      </c>
+      <c r="K3" s="14" t="n">
+        <v>4374.393</v>
+      </c>
+      <c r="L3" s="14" t="n">
+        <v>4374.393</v>
+      </c>
+      <c r="M3" s="12" t="n">
+        <v>175</v>
+      </c>
+      <c r="N3" s="14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="O3" s="12" t="n">
+        <v>517.7</v>
+      </c>
+      <c r="P3" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q3" s="13" t="inlineStr">
+        <is>
+          <t>Hit Take Profit (TP)</t>
+        </is>
+      </c>
+      <c r="R3" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>2577450981</v>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-21 07:44:54</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-21 07:51:02</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>6m 8d</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I4" s="11" t="n">
+        <v>4368.619</v>
+      </c>
+      <c r="J4" s="11" t="n">
+        <v>4363.431</v>
+      </c>
+      <c r="K4" s="11" t="n">
+        <v>4380.931</v>
+      </c>
+      <c r="L4" s="11" t="n">
+        <v>4362.783</v>
+      </c>
+      <c r="M4" s="9" t="n">
+        <v>-58.4</v>
+      </c>
+      <c r="N4" s="11" t="n">
+        <v>-5.84</v>
+      </c>
+      <c r="O4" s="9" t="n">
+        <v>511.86</v>
+      </c>
+      <c r="P4" s="9" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="Q4" s="10" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R4" s="10" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>2579837091</v>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:44:54</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:54:56</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>10m 2d</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>4357.664</v>
+      </c>
+      <c r="J5" s="11" t="n">
+        <v>4351.264</v>
+      </c>
+      <c r="K5" s="11" t="n">
+        <v>4373.664</v>
+      </c>
+      <c r="L5" s="11" t="n">
+        <v>4351.264</v>
+      </c>
+      <c r="M5" s="9" t="n">
+        <v>-64</v>
+      </c>
+      <c r="N5" s="11" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="O5" s="9" t="n">
+        <v>505.46</v>
+      </c>
+      <c r="P5" s="9" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="Q5" s="10" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R5" s="10" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>2583401048</v>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-22 03:29:55</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-22 05:08:10</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>1j 38m</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I6" s="14" t="n">
+        <v>4340.675</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>4336.175</v>
+      </c>
+      <c r="K6" s="14" t="n">
+        <v>4349.675</v>
+      </c>
+      <c r="L6" s="14" t="n">
+        <v>4349.675</v>
+      </c>
+      <c r="M6" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="N6" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="O6" s="12" t="n">
+        <v>514.46</v>
+      </c>
+      <c r="P6" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q6" s="13" t="inlineStr">
+        <is>
+          <t>Hit Take Profit (TP)</t>
+        </is>
+      </c>
+      <c r="R6" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>2584927512</v>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:14:55</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:19:50</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>1j 4m</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>4339.094</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>4332.394</v>
+      </c>
+      <c r="K7" s="14" t="n">
+        <v>4355.894</v>
+      </c>
+      <c r="L7" s="14" t="n">
+        <v>4339.294</v>
+      </c>
+      <c r="M7" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N7" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O7" s="12" t="n">
+        <v>514.66</v>
+      </c>
+      <c r="P7" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q7" s="13" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R7" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>2585747588</v>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-22 13:59:55</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-22 14:28:34</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>28m 39d</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>4318.927</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>4311.927</v>
+      </c>
+      <c r="K8" s="14" t="n">
+        <v>4336.427</v>
+      </c>
+      <c r="L8" s="14" t="n">
+        <v>4319.127</v>
+      </c>
+      <c r="M8" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O8" s="12" t="n">
+        <v>514.86</v>
+      </c>
+      <c r="P8" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q8" s="13" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R8" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>2587188646</v>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-22 17:59:55</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-22 18:55:35</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>55m 40d</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>4322.68</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>4329.969</v>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>4305.469</v>
+      </c>
+      <c r="L9" s="14" t="n">
+        <v>4322.48</v>
+      </c>
+      <c r="M9" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O9" s="12" t="n">
+        <v>515.0599999999999</v>
+      </c>
+      <c r="P9" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q9" s="13" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R9" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>2591745453</v>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:29:55</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23 15:10:44</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>40m 49d</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>4324.741</v>
+      </c>
+      <c r="J10" s="11" t="n">
+        <v>4317.487</v>
+      </c>
+      <c r="K10" s="11" t="n">
+        <v>4342.687</v>
+      </c>
+      <c r="L10" s="11" t="n">
+        <v>4317.487</v>
+      </c>
+      <c r="M10" s="9" t="n">
+        <v>-72.5</v>
+      </c>
+      <c r="N10" s="11" t="n">
+        <v>-7.25</v>
+      </c>
+      <c r="O10" s="9" t="n">
+        <v>507.81</v>
+      </c>
+      <c r="P10" s="9" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="Q10" s="10" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R10" s="10" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>2592236187</v>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23 16:44:54</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23 16:48:34</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>3m 40d</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>4316.467</v>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>4309.667</v>
+      </c>
+      <c r="K11" s="11" t="n">
+        <v>4333.467</v>
+      </c>
+      <c r="L11" s="11" t="n">
+        <v>4309.667</v>
+      </c>
+      <c r="M11" s="9" t="n">
+        <v>-68</v>
+      </c>
+      <c r="N11" s="11" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="O11" s="9" t="n">
+        <v>501.01</v>
+      </c>
+      <c r="P11" s="9" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="Q11" s="10" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R11" s="10" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>2592746187</v>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-23 18:44:54</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-23 18:48:07</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>3m 13d</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>4304.452</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>4297.352</v>
+      </c>
+      <c r="K12" s="14" t="n">
+        <v>4322.252</v>
+      </c>
+      <c r="L12" s="14" t="n">
+        <v>4304.652</v>
+      </c>
+      <c r="M12" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O12" s="12" t="n">
+        <v>501.21</v>
+      </c>
+      <c r="P12" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q12" s="13" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R12" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>2592820420</v>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-23 18:59:55</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:30:14</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>30m 19d</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>4309.479</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>4303.079</v>
+      </c>
+      <c r="K13" s="14" t="n">
+        <v>4322.279</v>
+      </c>
+      <c r="L13" s="14" t="n">
+        <v>4309.679</v>
+      </c>
+      <c r="M13" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N13" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O13" s="12" t="n">
+        <v>501.41</v>
+      </c>
+      <c r="P13" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q13" s="13" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R13" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>2593179348</v>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:54</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23 20:08:03</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>8m 9d</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>4310.338</v>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>4302.738</v>
+      </c>
+      <c r="K14" s="11" t="n">
+        <v>4325.538</v>
+      </c>
+      <c r="L14" s="11" t="n">
+        <v>4302.738</v>
+      </c>
+      <c r="M14" s="9" t="n">
+        <v>-76</v>
+      </c>
+      <c r="N14" s="11" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="O14" s="9" t="n">
+        <v>493.81</v>
+      </c>
+      <c r="P14" s="9" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="Q14" s="10" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R14" s="10" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>2595301847</v>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-24 02:59:55</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-24 06:43:32</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>3j 43m</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I15" s="14" t="n">
+        <v>4284.755</v>
+      </c>
+      <c r="J15" s="14" t="n">
+        <v>4276.255</v>
+      </c>
+      <c r="K15" s="14" t="n">
+        <v>4305.955</v>
+      </c>
+      <c r="L15" s="14" t="n">
+        <v>4284.955</v>
+      </c>
+      <c r="M15" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N15" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O15" s="12" t="n">
+        <v>494.01</v>
+      </c>
+      <c r="P15" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q15" s="13" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R15" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>2596572850</v>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-24 11:14:55</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:31:55</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>1j 17m</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <v>4285.272</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>4276.772</v>
+      </c>
+      <c r="K16" s="14" t="n">
+        <v>4306.472</v>
+      </c>
+      <c r="L16" s="14" t="n">
+        <v>4285.472</v>
+      </c>
+      <c r="M16" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N16" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O16" s="12" t="n">
+        <v>494.21</v>
+      </c>
+      <c r="P16" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q16" s="13" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R16" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>2596946151</v>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:59:54</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:35:57</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>36m 3d</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>4279.52</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>4271.42</v>
+      </c>
+      <c r="K17" s="14" t="n">
+        <v>4299.72</v>
+      </c>
+      <c r="L17" s="14" t="n">
+        <v>4279.72</v>
+      </c>
+      <c r="M17" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N17" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O17" s="12" t="n">
+        <v>494.41</v>
+      </c>
+      <c r="P17" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q17" s="13" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R17" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="12" t="n">
+        <v>2597157735</v>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:44:55</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:50:04</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>1j 5m</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I18" s="14" t="n">
+        <v>4278.702</v>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>4271.302</v>
+      </c>
+      <c r="K18" s="14" t="n">
+        <v>4297.202</v>
+      </c>
+      <c r="L18" s="14" t="n">
+        <v>4278.902</v>
+      </c>
+      <c r="M18" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N18" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O18" s="12" t="n">
+        <v>494.61</v>
+      </c>
+      <c r="P18" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q18" s="13" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R18" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>2597949075</v>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:14:55</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-24 16:30:23</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>15m 28d</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>4263.299</v>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>4254.865</v>
+      </c>
+      <c r="K19" s="11" t="n">
+        <v>4284.565</v>
+      </c>
+      <c r="L19" s="11" t="n">
+        <v>4254.865</v>
+      </c>
+      <c r="M19" s="9" t="n">
+        <v>-84.3</v>
+      </c>
+      <c r="N19" s="11" t="n">
+        <v>-8.43</v>
+      </c>
+      <c r="O19" s="9" t="n">
+        <v>486.18</v>
+      </c>
+      <c r="P19" s="9" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="Q19" s="10" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R19" s="10" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="12" t="n">
+        <v>2598448052</v>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-24 17:44:54</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-24 17:51:29</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>6m 35d</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I20" s="14" t="n">
+        <v>4259.055</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>4251.492</v>
+      </c>
+      <c r="K20" s="14" t="n">
+        <v>4274.292</v>
+      </c>
+      <c r="L20" s="14" t="n">
+        <v>4259.255</v>
+      </c>
+      <c r="M20" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N20" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O20" s="12" t="n">
+        <v>486.38</v>
+      </c>
+      <c r="P20" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q20" s="13" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R20" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="12" t="n">
+        <v>2600157994</v>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-24 22:44:54</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-24 22:55:44</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>10m 50d</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>4255.261</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>4247.661</v>
+      </c>
+      <c r="K21" s="14" t="n">
+        <v>4270.461</v>
+      </c>
+      <c r="L21" s="14" t="n">
+        <v>4255.461</v>
+      </c>
+      <c r="M21" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N21" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O21" s="12" t="n">
+        <v>486.58</v>
+      </c>
+      <c r="P21" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q21" s="13" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R21" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="12" t="n">
+        <v>2600228870</v>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-24 22:59:54</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:16:17</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>16m 23d</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I22" s="14" t="n">
+        <v>4256.853</v>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>4249.253</v>
+      </c>
+      <c r="K22" s="14" t="n">
+        <v>4272.053</v>
+      </c>
+      <c r="L22" s="14" t="n">
+        <v>4272.053</v>
+      </c>
+      <c r="M22" s="12" t="n">
+        <v>152</v>
+      </c>
+      <c r="N22" s="14" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="O22" s="12" t="n">
+        <v>501.78</v>
+      </c>
+      <c r="P22" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q22" s="13" t="inlineStr">
+        <is>
+          <t>Hit Take Profit (TP)</t>
+        </is>
+      </c>
+      <c r="R22" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="12" t="n">
+        <v>2600670946</v>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:59:54</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-25 01:25:34</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>1j 25m</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I23" s="14" t="n">
+        <v>4273.707</v>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>4282.596</v>
+      </c>
+      <c r="K23" s="14" t="n">
+        <v>4253.696</v>
+      </c>
+      <c r="L23" s="14" t="n">
+        <v>4273.507</v>
+      </c>
+      <c r="M23" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N23" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O23" s="12" t="n">
+        <v>501.98</v>
+      </c>
+      <c r="P23" s="12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="Q23" s="13" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+      <c r="R23" s="13" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="79" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Metrik Evaluasi Forward Testing</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Nilai Evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Nama Model</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF) (28 Fitur SMC/ICT + DXY + MTF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Metode Eksekusi</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Otomatis 0-Delay (MetaTrader 5 API)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Ambang Batas Keyakinan (Threshold)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Versi 4.1 (Structural RRR + Adaptive Hybrid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Target Forward Testing Skripsi</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>100 Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Saldo Awal Evaluasi</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>$500.00 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Saldo Terkini</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>$501.98 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Total Trade Otomatis Selesai</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>22 Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Progres Evaluasi (%)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>22.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Jumlah Trade WIN (Profit)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>16 Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Jumlah Trade LOSS (Rugi)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>6 Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Win Rate (%)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>72.73%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Total Akumulasi Profit ($ USD)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>$+1.98 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Return on Investment (ROI)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>+0.40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Rata-rata Profit per Trade</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>$+0.09 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Waktu Pembaruan Terakhir</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-26 03:55:08 WIB</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1478,7 +5002,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1700,7 +5224,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2786,7 +6310,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2972,7 +6496,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3528,226 +7052,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="81" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>Metrik Evaluasi Forward Testing</t>
-        </is>
-      </c>
-      <c r="B1" s="8" t="inlineStr">
-        <is>
-          <t>Nilai Evaluasi</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>Nama Model</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>LightGBM M15 v3.7 (Wide SL + RRR 2.5 + Sniper) (28 Fitur SMC/ICT + DXY + MTF)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Metode Eksekusi</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>Otomatis 0-Delay (MetaTrader 5 API)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Ambang Batas Keyakinan (Threshold)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Versi 3.7 (Wide SL + RRR 2.5 + Sniper Entry)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Target Forward Testing Skripsi</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>100 Trade</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Saldo Awal Evaluasi</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>$500.00 USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Saldo Terkini</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>$535.78 USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Total Trade Otomatis Selesai</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>6 Trade</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Progres Evaluasi (%)</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>6.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Jumlah Trade WIN (Profit)</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>4 Trade</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Jumlah Trade LOSS (Rugi)</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>2 Trade</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Win Rate (%)</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>66.67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Total Akumulasi Profit ($ USD)</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>$+35.78 USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Return on Investment (ROI)</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>+7.16%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Rata-rata Profit per Trade</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>$+5.96 USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>6.03</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Waktu Pembaruan Terakhir</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-17 23:54:14 WIB</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>